--- a/Result/profitability/3434.xlsx
+++ b/Result/profitability/3434.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1725</v>
+        <v>0.1625</v>
       </c>
       <c r="N2" t="n">
-        <v>19.39875</v>
+        <v>19.045</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.14375</v>
+        <v>0.105</v>
       </c>
       <c r="N3" t="n">
-        <v>18.8875</v>
+        <v>18.85625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11625</v>
+        <v>0.04375000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>18.40875</v>
+        <v>18.0975</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.09625</v>
       </c>
       <c r="N5" t="n">
-        <v>17.92875</v>
+        <v>18.1225</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09875</v>
+        <v>0.10625</v>
       </c>
       <c r="N6" t="n">
-        <v>17.34875</v>
+        <v>17.72625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02875</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>16.43875</v>
+        <v>16.6375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03875</v>
+        <v>-0.03624999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>16.06125</v>
+        <v>16.0175</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>140</v>
+      </c>
+      <c r="D75" t="n">
+        <v>113</v>
+      </c>
+      <c r="E75" t="n">
+        <v>27</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.16375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.3500000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01756146512794787</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.549999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.08596783139212416</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
